--- a/public/download/delete_user.xlsx
+++ b/public/download/delete_user.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\win-paloteo\public\download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD3C4BC-8467-4CDD-8E8E-C250296A5AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB4E497-5B8B-4C46-9842-82032D53A262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B58EF809-3A37-4D7C-BF5B-804219BF9F00}"/>
+    <workbookView xWindow="180" yWindow="-12120" windowWidth="16800" windowHeight="9675" xr2:uid="{B58EF809-3A37-4D7C-BF5B-804219BF9F00}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>tdoc</t>
   </si>
@@ -52,13 +52,16 @@
     <t>ce</t>
   </si>
   <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUENTES </t>
-  </si>
-  <si>
-    <t>ELI</t>
+    <t>12345678</t>
+  </si>
+  <si>
+    <t>AP PATERNO</t>
+  </si>
+  <si>
+    <t>AP MATERNO</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
   </si>
 </sst>
 </file>
@@ -445,7 +448,9 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="8.453125" customWidth="1"/>
     <col min="2" max="2" width="11.1796875" style="2" customWidth="1"/>
+    <col min="3" max="5" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -469,17 +474,17 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
-        <v>40214719</v>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
